--- a/testDjangosite/media/excel_files/listregion/listregion_527.xlsx
+++ b/testDjangosite/media/excel_files/listregion/listregion_527.xlsx
@@ -86,8 +86,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -463,152 +478,576 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L5"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+    <row r="0" ht="30" customHeight="1"/>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Перечетная ведомость участка №</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="1" t="n">
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Лесничество</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Локчимское</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Участковое лесничество</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Четдинское</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Урочище(дача)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>участок 3</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="n"/>
+      <c r="O3" s="1" t="n"/>
+      <c r="P3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Квартал</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Выдел</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Площадь га.</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="L4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+      <c r="P4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>кол-во ПП, шт</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>площадь 1 ПП</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>площадь ПП, га.</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n">
+        <v>3.125e-06</v>
+      </c>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+      <c r="P5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Номер пробной площади</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Искусственное восстановление</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Естественное возобновление (семенное)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Естественное возобновление (вегетативное)</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Порода</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>АБРИКОС сибирский</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Порода</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Порода</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Актинидия острая</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Макс высота</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Макс высота</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Макс высота</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Высота растений, м.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Высота растений, м.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Высота растений, м.</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>До 0,2</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0,21-0,5</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0,6-1,0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>1,1-1,5</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Более 1,5</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>До 0,2</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>0,21-0,5</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>0,6-1,0</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>1,1-1,5</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Более 1,5</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>До 0,2</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>0,21-0,5</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>0,6-1,0</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>1,1-1,5</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Более 1,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>571</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Итого:</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>на 1 Га</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>280000</v>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n">
+        <v>3230000</v>
+      </c>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="38">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="L7:P7"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G7:K7"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="L14:P14"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M9:P9"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
+    <mergeCell ref="L10:P10"/>
+    <mergeCell ref="G14:K14"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
@@ -634,163 +1073,163 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Перечетная ведомость участка №</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="1" t="n">
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="3" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Лесничество</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Локчимское</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Участковое лесничество</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Четдинское</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Урочище(дача)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>участок 3</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n"/>
+      <c r="L3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Квартал</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Выдел</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>Площадь га.</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="L4" s="4" t="n"/>
+      <c r="L4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>кол-во ПП, шт</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>площадь 1 ПП</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>площадь ПП, га.</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n">
+        <v>3.125e-06</v>
+      </c>
+      <c r="L5" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Подлесок</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>На 1 га</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
